--- a/templates/test_files/Strukturvorlage_AreaMgmt_v0.6.0.xlsx
+++ b/templates/test_files/Strukturvorlage_AreaMgmt_v0.6.0.xlsx
@@ -7888,7 +7888,7 @@
       </c>
       <c r="C105" s="159" t="inlineStr">
         <is>
-          <t>Der Objekttyp definiert die spezifischen Informationen zu einem Typ, die allen Instanzen dieses Typs gemeinsam sind.</t>
+          <t>Optionale IFC-TypeObject-Entität zur Dokumentation des Mapping-Umfangs. Leer = Mapping gilt nur für die Objektebene. Ausgefüllt = Mapping gilt zusätzlich für die angegebene Typebene; der Wert muss ein schema-konformes Paar mit „IfcObject Entity“ bilden (z. B. IfcTank → IfcTankType). Der PredefinedType wird separat erfasst und validiert.</t>
         </is>
       </c>
       <c r="F105" s="161" t="n"/>
@@ -10669,7 +10669,7 @@
       </c>
       <c r="Z2" s="71" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="AA2" s="71" t="inlineStr">
@@ -11137,7 +11137,7 @@
       </c>
       <c r="Z6" s="80" t="inlineStr">
         <is>
-          <t>validated against IFC 4.3 entity identifiers</t>
+          <t>Leer = nur Objektebene; ausgefüllt = Mapping gilt auch für die angegebene Typebene; validiert gegen IFC 4.3 Objekt-/TypeObject-Paare</t>
         </is>
       </c>
       <c r="AA6" s="80" t="inlineStr">
@@ -11246,11 +11246,7 @@
           <t>IfcBuildingStorey</t>
         </is>
       </c>
-      <c r="Z7" s="87" t="inlineStr">
-        <is>
-          <t>IfcBuildingStorey</t>
-        </is>
-      </c>
+      <c r="Z7" s="87" t="n"/>
       <c r="AA7" s="87" t="n"/>
       <c r="AB7" s="87" t="n"/>
       <c r="AC7" s="130" t="n"/>
@@ -11366,11 +11362,7 @@
           <t>IfcSite</t>
         </is>
       </c>
-      <c r="Z8" s="87" t="inlineStr">
-        <is>
-          <t>IfcSite</t>
-        </is>
-      </c>
+      <c r="Z8" s="87" t="n"/>
       <c r="AA8" s="87" t="n"/>
       <c r="AB8" s="87" t="n"/>
       <c r="AC8" s="130" t="n"/>
@@ -11488,7 +11480,7 @@
       </c>
       <c r="Z9" s="87" t="inlineStr">
         <is>
-          <t>IfcSpace</t>
+          <t>IfcSpaceType</t>
         </is>
       </c>
       <c r="AA9" s="87" t="inlineStr">
@@ -11616,7 +11608,7 @@
       </c>
       <c r="Z10" s="87" t="inlineStr">
         <is>
-          <t>IfcSpace</t>
+          <t>IfcSpaceType</t>
         </is>
       </c>
       <c r="AA10" s="87" t="inlineStr">
@@ -11744,7 +11736,7 @@
       </c>
       <c r="Z11" s="87" t="inlineStr">
         <is>
-          <t>IfcSpace</t>
+          <t>IfcSpaceType</t>
         </is>
       </c>
       <c r="AA11" s="87" t="inlineStr">
@@ -11868,7 +11860,7 @@
       </c>
       <c r="Z12" s="87" t="inlineStr">
         <is>
-          <t>IfcSpace</t>
+          <t>IfcSpaceType</t>
         </is>
       </c>
       <c r="AA12" s="87" t="inlineStr">
@@ -11996,7 +11988,7 @@
       </c>
       <c r="Z13" s="87" t="inlineStr">
         <is>
-          <t>IfcSpace</t>
+          <t>IfcSpaceType</t>
         </is>
       </c>
       <c r="AA13" s="87" t="inlineStr">
@@ -12124,7 +12116,7 @@
       </c>
       <c r="Z14" s="87" t="inlineStr">
         <is>
-          <t>IfcSpace</t>
+          <t>IfcSpaceType</t>
         </is>
       </c>
       <c r="AA14" s="87" t="inlineStr">

--- a/templates/test_files/Strukturvorlage_AreaMgmt_v0.6.0.xlsx
+++ b/templates/test_files/Strukturvorlage_AreaMgmt_v0.6.0.xlsx
@@ -8910,7 +8910,7 @@
       </c>
       <c r="C140" s="169" t="inlineStr">
         <is>
-          <t>Beschreibt eine Liste von Merkmalen / Mebgeb für eine IFC-Entität. Merkmalssätze / Mengensätze, deren Struktur und Eigenschaften fest in der IFC-Spezifikation definiert sind.</t>
+          <t>Referenz auf einen IFC-Merkmals- oder Mengensatz. Ein Einzelwert wird direkt als Pset_*/Qto_*-Name oder zulässige absolute IRI erfasst. Mehrere Werte müssen als gültige JSON-Liste aus nicht leeren Strings mit doppelten Anführungszeichen erfasst werden, z. B. ["Pset_WallCommon", "Qto_WallBaseQuantities"]. Zeilenumbruch-, Semikolon- und einfache Kommalisten sind nicht zulässig.</t>
         </is>
       </c>
       <c r="F140" s="161" t="n"/>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="X6" s="80" t="inlineStr">
         <is>
-          <t>validated against IFC 4.3 property/quantity set identifiers when IFC_URI is present</t>
+          <t>Ein Wert: Pset_* / Qto_* oder zulässige absolute IRI. Mehrere Werte: strikte JSON-Liste, z. B. ["Pset_WallCommon", "Qto_WallBaseQuantities"]; keine Zeilenumbruch-/Semikolonlisten.</t>
         </is>
       </c>
       <c r="Y6" s="80" t="inlineStr">
